--- a/Config/Datas/npc_view_randomization.xlsx
+++ b/Config/Datas/npc_view_randomization.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>civil_variant_01</t>
+          <t>civil_view_01</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>civil_variant_02</t>
+          <t>civil_view_02</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>civil_variant_03</t>
+          <t>civil_view_03</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>civil_variant_01</t>
+          <t>civil_view_01</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -573,7 +573,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>civil_variant_02</t>
+          <t>civil_view_02</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>civil_variant_03</t>
+          <t>civil_view_03</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>civil_variant_01</t>
+          <t>civil_view_01</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -618,7 +618,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>civil_variant_02</t>
+          <t>civil_view_02</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>civil_variant_03</t>
+          <t>civil_view_03</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>civil_variant_01</t>
+          <t>civil_view_01</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>civil_variant_02</t>
+          <t>civil_view_02</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>civil_variant_03</t>
+          <t>civil_view_03</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -693,7 +693,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>civil_variant_01</t>
+          <t>civil_view_01</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>civil_variant_02</t>
+          <t>civil_view_02</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>civil_variant_03</t>
+          <t>civil_view_03</t>
         </is>
       </c>
       <c r="D19" t="n">
